--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/VIRGINIA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/VIRGINIA_2013.xlsx
@@ -1914,7 +1914,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C87">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C194">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C493">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C552">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C574">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C936">
